--- a/Data/27/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -250,7 +250,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699399</t>
+    <t>10699531</t>
   </si>
   <si>
     <t>Passed</t>
@@ -262,10 +262,10 @@
     <t>Romania</t>
   </si>
   <si>
-    <t>Henry</t>
-  </si>
-  <si>
-    <t>Jast</t>
+    <t>Xavier</t>
+  </si>
+  <si>
+    <t>Bogan</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -355,7 +355,7 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1630206286769</t>
+    <t>1630206286770</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -409,19 +409,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699400</t>
+    <t>10699532</t>
   </si>
   <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Dallas</t>
-  </si>
-  <si>
-    <t>Fadel</t>
-  </si>
-  <si>
-    <t>Auto 24512660</t>
+    <t>Jett</t>
+  </si>
+  <si>
+    <t>Gusikowski</t>
+  </si>
+  <si>
+    <t>Auto 5975198</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -436,7 +436,7 @@
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t>1321228095500</t>
+    <t>1321228095501</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K2" s="17">
         <f>TODAY()-100</f>
-        <v>45704</v>
+        <v>45710</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>81</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="W2" s="17">
         <f>TODAY()-100</f>
-        <v>45704</v>
+        <v>45710</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>92</v>
@@ -1439,11 +1439,11 @@
       </c>
       <c r="AY2" s="17">
         <f>TODAY()-100</f>
-        <v>45704</v>
+        <v>45710</v>
       </c>
       <c r="AZ2" s="17">
         <f>TODAY()-100</f>
-        <v>45704</v>
+        <v>45710</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>100</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="BI2" s="16">
         <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>947782</v>
+        <v>934819</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>114</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="K3" s="34" t="str">
         <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>16/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>81</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="W3" s="34" t="str">
         <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>16/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>92</v>
@@ -1693,11 +1693,11 @@
       </c>
       <c r="AY3" s="34" t="str">
         <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>16/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
         <f t="shared" si="3"/>
-        <v>16/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
@@ -1725,7 +1725,7 @@
         <v>116</v>
       </c>
       <c r="BI3" s="16">
-        <v>317469</v>
+        <v>247847</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>114</v>

--- a/Data/27/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{84683DE0-2CB3-4F0E-86C4-A2B63A20BFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="134">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -250,24 +265,12 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699531</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>880 Recruitment (Vofur Hagovi (10551546))</t>
   </si>
   <si>
     <t>Romania</t>
   </si>
   <si>
-    <t>Xavier</t>
-  </si>
-  <si>
-    <t>Bogan</t>
-  </si>
-  <si>
     <t>Mobile</t>
   </si>
   <si>
@@ -355,9 +358,6 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1630206286770</t>
-  </si>
-  <si>
     <t>01/01/2000</t>
   </si>
   <si>
@@ -409,18 +409,9 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699532</t>
-  </si>
-  <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Jett</t>
-  </si>
-  <si>
-    <t>Gusikowski</t>
-  </si>
-  <si>
     <t>Auto 5975198</t>
   </si>
   <si>
@@ -430,63 +421,66 @@
     <t>Part Time</t>
   </si>
   <si>
-    <t xml:space="preserve">92 Retail Management </t>
+    <t>92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t>1321228095501</t>
+    <t>1630206286771</t>
+  </si>
+  <si>
+    <t>1321228095502</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="4"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -529,8 +523,12 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -540,17 +538,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -948,9 +956,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CD3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.81640625" style="1" customWidth="1"/>
@@ -1032,10 +1040,11 @@
     <col min="80" max="80" width="8.1796875" style="1" customWidth="1"/>
     <col min="81" max="81" width="11.453125" style="1" customWidth="1"/>
     <col min="82" max="82" width="12.08984375" style="1" customWidth="1"/>
-    <col min="83" max="16384" width="8.7265625" style="3" customWidth="1"/>
+    <col min="83" max="83" width="8.7265625" style="3" customWidth="1"/>
+    <col min="84" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:82" s="4" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:82" s="4" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1283,92 +1292,84 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:82" s="10" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>83</v>
-      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="16">
         <v>720527700</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K2" s="17">
-        <f>TODAY()-100</f>
-        <v>45710</v>
+        <f ca="1">TODAY()-100</f>
+        <v>45717</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N2" s="16">
         <v>1</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P2" s="16">
         <v>515100</v>
       </c>
       <c r="Q2" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="V2" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="W2" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45717</v>
+      </c>
+      <c r="X2" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="Y2" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="S2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="19" t="s">
+      <c r="Z2" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="AA2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="V2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="W2" s="17">
-        <f>TODAY()-100</f>
-        <v>45710</v>
-      </c>
-      <c r="X2" s="16" t="s">
+      <c r="AB2" s="23" t="s">
         <v>92</v>
-      </c>
-      <c r="Y2" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z2" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA2" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB2" s="23" t="s">
-        <v>96</v>
       </c>
       <c r="AC2" s="21">
         <v>880</v>
@@ -1377,252 +1378,244 @@
         <v>61</v>
       </c>
       <c r="AE2" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF2" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG2" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH2" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI2" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AF2" s="25" t="s">
+      <c r="AJ2" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="AG2" s="14" t="s">
+      <c r="AK2" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="AH2" s="26" t="s">
+      <c r="AL2" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="AI2" s="16" t="s">
+      <c r="AM2" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="AJ2" s="27" t="s">
+      <c r="AN2" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="AK2" s="21" t="s">
+      <c r="AO2" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="AL2" s="16" t="s">
+      <c r="AP2" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AM2" s="16" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="AN2" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO2" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="AP2" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ2" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR2" s="14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AS2" s="16">
         <v>1</v>
       </c>
-      <c r="AT2" s="17">
-        <f t="shared" ref="AT2:AT3" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>NaN</v>
+      <c r="AT2" s="17" t="str">
+        <f t="shared" ref="AT2:AT3" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>01/03/2025</v>
       </c>
       <c r="AU2" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AV2" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AW2" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AX2" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45717</v>
+      </c>
+      <c r="AZ2" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45717</v>
+      </c>
+      <c r="BA2" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB2" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC2" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD2" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE2" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF2" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="18" t="s">
+      <c r="BG2" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH2" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="17">
-        <f>TODAY()-100</f>
-        <v>45710</v>
-      </c>
-      <c r="AZ2" s="17">
-        <f>TODAY()-100</f>
-        <v>45710</v>
-      </c>
-      <c r="BA2" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BC2" s="30" t="s">
+      <c r="BI2" s="16">
+        <f t="array" aca="1" ref="BI2:BI3" ca="1">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
+        <v>448559</v>
+      </c>
+      <c r="BJ2" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BK2" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL2" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM2" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN2" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="BD2" s="31" t="s">
+      <c r="BO2" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="BE2" s="19" t="s">
+      <c r="BP2" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="BF2" s="19" t="s">
+      <c r="BQ2" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BR2" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG2" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH2" s="30" t="s">
+      <c r="BS2" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="BT2" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="BI2" s="16">
-        <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>934819</v>
-      </c>
-      <c r="BJ2" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK2" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL2" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM2" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN2" s="32" t="s">
+      <c r="BU2" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV2" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="BO2" s="32" t="s">
+      <c r="BW2" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="BP2" s="32" t="s">
+      <c r="BX2" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="BQ2" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR2" s="32" t="s">
+      <c r="BY2" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="BS2" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT2" s="29" t="s">
+      <c r="BZ2" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU2" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV2" s="33" t="s">
+      <c r="CA2" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW2" s="33" t="s">
+      <c r="CB2" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC2" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX2" s="29" t="s">
+      <c r="CD2" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="BY2" s="29" t="s">
+    </row>
+    <row r="3" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="BZ2" s="29" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="CA2" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB2" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC2" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CD2" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>134</v>
-      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
       <c r="H3" s="16">
         <v>720527700</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K3" s="34" t="str">
-        <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>22/02/2025</v>
+        <f t="shared" ref="K3" ca="1" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>01/03/2025</v>
       </c>
       <c r="L3" s="32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M3" s="29" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N3" s="29">
         <v>1</v>
       </c>
       <c r="O3" s="29" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P3" s="29">
         <v>515100</v>
       </c>
       <c r="Q3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="R3" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="T3" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="U3" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="V3" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="W3" s="34" t="str">
+        <f t="shared" ref="W3" ca="1" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>01/03/2025</v>
+      </c>
+      <c r="X3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="S3" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" s="32" t="s">
+      <c r="Y3" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z3" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="U3" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="W3" s="34" t="str">
-        <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>22/02/2025</v>
-      </c>
-      <c r="X3" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y3" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z3" s="23" t="s">
-        <v>94</v>
-      </c>
       <c r="AA3" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AB3" s="36" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="AC3" s="21">
         <v>880</v>
@@ -1634,193 +1627,179 @@
         <v>35</v>
       </c>
       <c r="AF3" s="25" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AG3" s="14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AH3" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI3" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ3" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK3" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="AL3" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="AI3" s="16" t="s">
+      <c r="AM3" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="AJ3" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="AK3" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL3" s="16" t="s">
+      <c r="AN3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO3" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="AP3" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="AM3" s="16" t="s">
+      <c r="AQ3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="AN3" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO3" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="AP3" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ3" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR3" s="14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AS3" s="16">
         <v>2</v>
       </c>
-      <c r="AT3" s="17">
-        <f t="shared" si="0"/>
-        <v>NaN</v>
+      <c r="AT3" s="17" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>01/03/2025</v>
       </c>
       <c r="AU3" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AW3" s="32" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AX3" s="29" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AY3" s="34" t="str">
-        <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>22/02/2025</v>
+        <f t="shared" ref="AY3:AZ3" ca="1" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>01/03/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
-        <f t="shared" si="3"/>
-        <v>22/02/2025</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>01/03/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
         <v>N/A</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BC3" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD3" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="BE3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF3" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="BG3" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH3" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="BI3" s="16">
+        <f ca="1"/>
+        <v>968129</v>
+      </c>
+      <c r="BJ3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BK3" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL3" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM3" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN3" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="BD3" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="BE3" s="19" t="s">
+      <c r="BO3" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="BP3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BQ3" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BR3" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG3" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH3" s="30" t="s">
+      <c r="BS3" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="BT3" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="BI3" s="16">
-        <v>247847</v>
-      </c>
-      <c r="BJ3" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK3" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL3" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM3" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN3" s="32" t="s">
+      <c r="BU3" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV3" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="BO3" s="32" t="s">
+      <c r="BW3" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="BP3" s="19" t="s">
+      <c r="BX3" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="BQ3" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR3" s="32" t="s">
+      <c r="BY3" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="BS3" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT3" s="29" t="s">
+      <c r="BZ3" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU3" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV3" s="32" t="s">
+      <c r="CA3" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW3" s="32" t="s">
+      <c r="CB3" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC3" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX3" s="29" t="s">
+      <c r="CD3" s="29" t="s">
         <v>124</v>
-      </c>
-      <c r="BY3" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="BZ3" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="CA3" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB3" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CD3" s="29" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3 X2:X3 V2:V3 S2:S3 BX2:BX3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX2:BX3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3 J2:J3" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
-      <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1"/>
-    <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/27/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{84683DE0-2CB3-4F0E-86C4-A2B63A20BFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="141">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -265,12 +250,24 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>10699766</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>880 Recruitment (Vofur Hagovi (10551546))</t>
   </si>
   <si>
     <t>Romania</t>
   </si>
   <si>
+    <t>Cecile</t>
+  </si>
+  <si>
+    <t>Runolfsdottir</t>
+  </si>
+  <si>
     <t>Mobile</t>
   </si>
   <si>
@@ -358,6 +355,9 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
+    <t>1630206286815</t>
+  </si>
+  <si>
     <t>01/01/2000</t>
   </si>
   <si>
@@ -409,10 +409,19 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10699767</t>
+  </si>
+  <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Auto 5975198</t>
+    <t>Keven</t>
+  </si>
+  <si>
+    <t>Hudson</t>
+  </si>
+  <si>
+    <t>Auto 56191697</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -421,69 +430,66 @@
     <t>Part Time</t>
   </si>
   <si>
-    <t>92 Retail Management </t>
+    <t xml:space="preserve">92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t>1630206286771</t>
-  </si>
-  <si>
-    <t>1321228095502</t>
+    <t>1630206286816</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="4"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="4"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,6 +513,11 @@
         <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -523,12 +534,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -538,27 +545,17 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -653,14 +650,14 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -956,12 +953,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CD3"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="63.54296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="31" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.1796875" style="1" customWidth="1"/>
@@ -1040,11 +1037,10 @@
     <col min="80" max="80" width="8.1796875" style="1" customWidth="1"/>
     <col min="81" max="81" width="11.453125" style="1" customWidth="1"/>
     <col min="82" max="82" width="12.08984375" style="1" customWidth="1"/>
-    <col min="83" max="83" width="8.7265625" style="3" customWidth="1"/>
-    <col min="84" max="16384" width="8.7265625" style="3"/>
+    <col min="83" max="16384" width="8.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" s="4" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:82" s="4" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1292,84 +1288,92 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:82" s="10" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="D2" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>83</v>
+      </c>
       <c r="H2" s="16">
         <v>720527700</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J2" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="17">
+        <f>TODAY()-100</f>
+        <v>45727</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="17">
-        <f ca="1">TODAY()-100</f>
-        <v>45717</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>79</v>
-      </c>
       <c r="M2" s="18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N2" s="16">
         <v>1</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="P2" s="16">
         <v>515100</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R2" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="S2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="S2" s="16" t="s">
-        <v>81</v>
-      </c>
       <c r="T2" s="19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="V2" s="16" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="W2" s="17">
-        <f ca="1">TODAY()-100</f>
-        <v>45717</v>
+        <f>TODAY()-100</f>
+        <v>45727</v>
       </c>
       <c r="X2" s="16" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Y2" s="19" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Z2" s="21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AA2" s="22" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AB2" s="23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AC2" s="21">
         <v>880</v>
@@ -1378,244 +1382,252 @@
         <v>61</v>
       </c>
       <c r="AE2" s="24" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AF2" s="25" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG2" s="14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AH2" s="26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AI2" s="16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AJ2" s="27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK2" s="21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AL2" s="16" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AM2" s="16" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AN2" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AO2" s="28" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AP2" s="29" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AQ2" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AR2" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AS2" s="16">
         <v>1</v>
       </c>
-      <c r="AT2" s="17" t="str">
-        <f t="shared" ref="AT2:AT3" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>01/03/2025</v>
+      <c r="AT2" s="17">
+        <f t="shared" ref="AT2:AT3" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>NaN</v>
       </c>
       <c r="AU2" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AV2" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AW2" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AX2" s="18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AY2" s="17">
-        <f ca="1">TODAY()-100</f>
-        <v>45717</v>
+        <f>TODAY()-100</f>
+        <v>45727</v>
       </c>
       <c r="AZ2" s="17">
-        <f ca="1">TODAY()-100</f>
-        <v>45717</v>
+        <f>TODAY()-100</f>
+        <v>45727</v>
       </c>
       <c r="BA2" s="26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="BB2" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BC2" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE2" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF2" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG2" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH2" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI2" s="16">
+        <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
+        <v>864534</v>
+      </c>
+      <c r="BJ2" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK2" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BL2" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM2" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN2" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO2" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="BP2" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ2" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR2" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS2" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT2" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU2" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV2" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW2" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX2" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BY2" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="BZ2" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CA2" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB2" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="CC2" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD2" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="BC2" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD2" s="31" t="s">
+      <c r="D3" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="BE2" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="BF2" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="BG2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH2" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="BI2" s="16">
-        <f t="array" aca="1" ref="BI2:BI3" ca="1">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>448559</v>
-      </c>
-      <c r="BJ2" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="BK2" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="BL2" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="BM2" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN2" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="BO2" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="BP2" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="BQ2" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="BR2" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="BS2" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT2" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="BU2" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="BV2" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW2" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX2" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="BY2" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="BZ2" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="CA2" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="CB2" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="CC2" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="CD2" s="29" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="E3" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>134</v>
+      </c>
       <c r="H3" s="16">
         <v>720527700</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J3" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="34" t="str">
+        <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>11/03/2025</v>
+      </c>
+      <c r="L3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="34" t="str">
-        <f t="shared" ref="K3" ca="1" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>01/03/2025</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>79</v>
-      </c>
       <c r="M3" s="29" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N3" s="29">
         <v>1</v>
       </c>
       <c r="O3" s="29" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="P3" s="29">
         <v>515100</v>
       </c>
       <c r="Q3" s="29" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R3" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="S3" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="S3" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="T3" s="32" t="s">
-        <v>86</v>
+      <c r="T3" s="31" t="s">
+        <v>90</v>
       </c>
       <c r="U3" s="35" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="V3" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="W3" s="34" t="str">
-        <f t="shared" ref="W3" ca="1" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>01/03/2025</v>
+        <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>11/03/2025</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="Z3" s="23" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AA3" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="AB3" s="36" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="AC3" s="21">
         <v>880</v>
@@ -1627,179 +1639,193 @@
         <v>35</v>
       </c>
       <c r="AF3" s="25" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG3" s="14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AH3" s="37" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AI3" s="16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AJ3" s="38" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="AK3" s="39" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AL3" s="16" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AM3" s="16" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AN3" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AO3" s="28" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AP3" s="28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AQ3" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AR3" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AS3" s="16">
         <v>2</v>
       </c>
-      <c r="AT3" s="17" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>01/03/2025</v>
+      <c r="AT3" s="17">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
       </c>
       <c r="AU3" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW3" s="32" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="AW3" s="31" t="s">
+        <v>110</v>
       </c>
       <c r="AX3" s="29" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AY3" s="34" t="str">
-        <f t="shared" ref="AY3:AZ3" ca="1" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>01/03/2025</v>
+        <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>11/03/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>01/03/2025</v>
+        <f t="shared" si="3"/>
+        <v>11/03/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
         <v>N/A</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BC3" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD3" s="31" t="s">
-        <v>133</v>
+        <v>112</v>
+      </c>
+      <c r="BD3" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="BE3" s="19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BF3" s="19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BG3" s="30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BH3" s="30" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BI3" s="16">
-        <f ca="1"/>
-        <v>968129</v>
+        <v>221911</v>
       </c>
       <c r="BJ3" s="19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BK3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="BL3" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="BM3" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN3" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="BO3" s="32" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="BL3" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM3" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN3" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO3" s="31" t="s">
+        <v>118</v>
       </c>
       <c r="BP3" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BQ3" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="BR3" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="BS3" s="32" t="s">
-        <v>96</v>
+        <v>119</v>
+      </c>
+      <c r="BQ3" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR3" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS3" s="31" t="s">
+        <v>100</v>
       </c>
       <c r="BT3" s="29" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BU3" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="BV3" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="32" t="s">
-        <v>118</v>
+        <v>81</v>
+      </c>
+      <c r="BV3" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW3" s="31" t="s">
+        <v>123</v>
       </c>
       <c r="BX3" s="29" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="BY3" s="29" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="BZ3" s="29" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="CA3" s="29" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="CB3" s="29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="CC3" s="29" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="CD3" s="29" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3 X2:X3 V2:V3 S2:S3 BX2:BX3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3 J2:J3" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX2:BX3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3">
       <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
+      <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>
